--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>366</v>
+        <v>280</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="E2">
+        <v>43</v>
+      </c>
+      <c r="G2">
         <v>0</v>
-      </c>
-      <c r="G2">
-        <v>52</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>212</v>
+        <v>393</v>
       </c>
       <c r="D3">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D2">
         <v>103</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>426</v>
